--- a/JsonFile/Assets/ExcelFiles/Merchant's items.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Merchant's items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27ED41D7-2A93-4BFE-8DFE-498BE25E1533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565118F4-FE9D-41F1-A4AA-843408949931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,10 +30,6 @@
     <t>Weapon_Name</t>
   </si>
   <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Item_Price</t>
   </si>
   <si>
@@ -389,6 +385,10 @@
   </si>
   <si>
     <t>Item_ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Type</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -841,8 +841,8 @@
     <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.875" bestFit="1" customWidth="1"/>
@@ -858,16 +858,16 @@
   <sheetData>
     <row r="1" spans="1:16" ht="18">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -883,13 +883,13 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -907,13 +907,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -931,13 +931,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>9</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -955,13 +955,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -979,13 +979,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="C6" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1027,13 +1027,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1051,13 +1051,13 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>19</v>
-      </c>
       <c r="C9" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1075,13 +1075,13 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>21</v>
-      </c>
       <c r="C10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1099,13 +1099,13 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="C11" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1123,13 +1123,13 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="C12" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1147,13 +1147,13 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="C13" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -1190,13 +1190,13 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="C15" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -1208,13 +1208,13 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="C16" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1226,13 +1226,13 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="C17" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1244,13 +1244,13 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>38</v>
-      </c>
       <c r="C18" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1262,13 +1262,13 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="C19" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1280,13 +1280,13 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="C20" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1298,13 +1298,13 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>44</v>
-      </c>
       <c r="C21" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -1316,13 +1316,13 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>46</v>
-      </c>
       <c r="C22" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -1334,13 +1334,13 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>48</v>
-      </c>
       <c r="C23" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>7</v>

--- a/JsonFile/Assets/ExcelFiles/Merchant's items.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Merchant's items.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565118F4-FE9D-41F1-A4AA-843408949931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D87FFF-6317-42A2-9AA2-CA4541F689F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BlackSmith" sheetId="1" r:id="rId1"/>
+    <sheet name="General" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
-  <si>
-    <t>Weapon_Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
   <si>
     <t>Item_Price</t>
   </si>
@@ -389,6 +387,153 @@
   </si>
   <si>
     <t>Item_Type</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간 포션</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_002</t>
+  </si>
+  <si>
+    <t>삽</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_003</t>
+  </si>
+  <si>
+    <t>곡괭이</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_004</t>
+  </si>
+  <si>
+    <t>나무사다리</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_005</t>
+  </si>
+  <si>
+    <t>쓰레기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_006</t>
+  </si>
+  <si>
+    <t>도로롱인형</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_007</t>
+  </si>
+  <si>
+    <t>테스트1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_008</t>
+  </si>
+  <si>
+    <t>테스트2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_009</t>
+  </si>
+  <si>
+    <t>테스트3</t>
+  </si>
+  <si>
+    <t>Item_010</t>
+  </si>
+  <si>
+    <t>테스트4</t>
+  </si>
+  <si>
+    <t>Item_011</t>
+  </si>
+  <si>
+    <t>테스트5</t>
+  </si>
+  <si>
+    <t>Item_012</t>
+  </si>
+  <si>
+    <t>테스트6</t>
+  </si>
+  <si>
+    <t>Item_013</t>
+  </si>
+  <si>
+    <t>테스트7</t>
+  </si>
+  <si>
+    <t>Item_014</t>
+  </si>
+  <si>
+    <t>테스트8</t>
+  </si>
+  <si>
+    <t>Item_015</t>
+  </si>
+  <si>
+    <t>테스트9</t>
+  </si>
+  <si>
+    <t>Item_016</t>
+  </si>
+  <si>
+    <t>테스트10</t>
+  </si>
+  <si>
+    <t>Item_017</t>
+  </si>
+  <si>
+    <t>테스트11</t>
+  </si>
+  <si>
+    <t>Item_018</t>
+  </si>
+  <si>
+    <t>테스트12</t>
+  </si>
+  <si>
+    <t>Item_019</t>
+  </si>
+  <si>
+    <t>테스트13</t>
+  </si>
+  <si>
+    <t>Item_020</t>
+  </si>
+  <si>
+    <t>테스트14</t>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Price</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable</t>
+  </si>
+  <si>
+    <t>Item_Name</t>
+  </si>
+  <si>
+    <t>Item_Name</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -533,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -554,6 +699,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -858,16 +1004,16 @@
   <sheetData>
     <row r="1" spans="1:16" ht="18">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -883,13 +1029,13 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -907,13 +1053,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>6</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -931,13 +1077,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="C4" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -955,13 +1101,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>10</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -979,13 +1125,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="C6" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1003,13 +1149,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1027,13 +1173,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1051,13 +1197,13 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="C9" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1075,13 +1221,13 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>20</v>
-      </c>
       <c r="C10" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1099,13 +1245,13 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="C11" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1123,13 +1269,13 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="C12" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -1147,13 +1293,13 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="C13" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1171,13 +1317,13 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -1190,13 +1336,13 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="C15" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>10</v>
@@ -1208,13 +1354,13 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="C16" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1226,13 +1372,13 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>35</v>
-      </c>
       <c r="C17" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -1244,13 +1390,13 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>37</v>
-      </c>
       <c r="C18" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -1262,13 +1408,13 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>39</v>
-      </c>
       <c r="C19" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1280,13 +1426,13 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="C20" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1298,13 +1444,13 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>43</v>
-      </c>
       <c r="C21" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -1316,13 +1462,13 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>45</v>
-      </c>
       <c r="C22" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -1334,13 +1480,13 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="C23" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>7</v>
@@ -1374,4 +1520,314 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA62FE8-7B60-4F43-A55D-C6DDB353700F}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/JsonFile/Assets/ExcelFiles/Merchant's items.xlsx
+++ b/JsonFile/Assets/ExcelFiles/Merchant's items.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김태경\Documents\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Adventure\JsonFile\Assets\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D87FFF-6317-42A2-9AA2-CA4541F689F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1237A253-97C0-416D-9173-8F602D62B52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="705" yWindow="2415" windowWidth="38160" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BlackSmith" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1134,7 +1137,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
